--- a/DesignData/Excel_Masters/ArmorStats_Master.xlsx
+++ b/DesignData/Excel_Masters/ArmorStats_Master.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\UnrealCpp\Paradise\DesignData\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\KGA\Documents\Unreal Projects\ProjectParadise\DesignData\Excel_Masters\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -26,10 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
-  <si>
-    <t>---</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="79">
   <si>
     <t>DefensePower</t>
   </si>
@@ -50,10 +47,6 @@
   </si>
   <si>
     <t>LevelUpCostId</t>
-  </si>
-  <si>
-    <t>ArmorTag</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>Item.Type.Armor.Helmet</t>
@@ -72,10 +65,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Rarity</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Common</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -96,22 +85,193 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Iron_Helmet</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Item.Type.Armor.Helmet</t>
-  </si>
-  <si>
-    <t>철 헬멧</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>철 헬멧 입니다</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Common</t>
+  </si>
+  <si>
+    <t>Armor_Displacer</t>
+  </si>
+  <si>
+    <t>Armor_Rescue</t>
+  </si>
+  <si>
+    <t>Armor_HazmatSuit</t>
+  </si>
+  <si>
+    <t>Armor_Raiders</t>
+  </si>
+  <si>
+    <t>Armor_BishopsRobe</t>
+  </si>
+  <si>
+    <t>Armor_Webrunner</t>
+  </si>
+  <si>
+    <t>Hat_Bluerose</t>
+  </si>
+  <si>
+    <t>Hat_Angela</t>
+  </si>
+  <si>
+    <t>Hat_Tiara</t>
+  </si>
+  <si>
+    <t>Hat_FeliceHat</t>
+  </si>
+  <si>
+    <t>Necklace_ButterflyDance</t>
+  </si>
+  <si>
+    <t>Necklace_NecklaceOfGuide</t>
+  </si>
+  <si>
+    <t>Necklace_NecklaceOfAmplify</t>
+  </si>
+  <si>
+    <t>Necklace_PendantOfPassion</t>
+  </si>
+  <si>
+    <t>Ring_RingOfWarrior</t>
+  </si>
+  <si>
+    <t>Ring_RingOfAssassin</t>
+  </si>
+  <si>
+    <t>Ring_RingOfHunter</t>
+  </si>
+  <si>
+    <t>Ring_RingOfCommander</t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>Rarity</t>
+  </si>
+  <si>
+    <t>디스플레이서의 갑옷</t>
+  </si>
+  <si>
+    <t>공간을 일그러뜨려 공격을 빗나가게 만드는 신비한 갑옷입니다.</t>
+  </si>
+  <si>
+    <t>Epic</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>Cost_Epic</t>
+  </si>
+  <si>
+    <t>구조대원의 방호복</t>
+  </si>
+  <si>
+    <t>극한의 환경에서도 생존할 수 있도록 튼튼하게 설계되었습니다.</t>
+  </si>
+  <si>
+    <t>Rare</t>
+  </si>
+  <si>
+    <t>Cost_Rare</t>
+  </si>
+  <si>
+    <t>위험물 처리복</t>
+  </si>
+  <si>
+    <t>유독 물질과 물리적 충격으로부터 몸을 보호합니다.</t>
+  </si>
+  <si>
+    <t>레이더의 가죽 갑옷</t>
+  </si>
+  <si>
+    <t>거친 황무지를 누비는 자들이 입는 질긴 가죽옷입니다.</t>
+  </si>
+  <si>
+    <t>Cost_Normal</t>
+  </si>
+  <si>
+    <t>주교의 로브</t>
+  </si>
+  <si>
+    <t>성스러운 기운이 서려 있어 정신력을 크게 높여줍니다.</t>
+  </si>
+  <si>
+    <t>웹러너의 재킷</t>
+  </si>
+  <si>
+    <t>사이버 스페이스를 유영하는 해커들이 즐겨 입는 기능성 재킷입니다.</t>
+  </si>
+  <si>
+    <t>푸른 장미의 모자</t>
+  </si>
+  <si>
+    <t>밤의 귀족들이 쓰던 우아한 장식이 달린 모자입니다.</t>
+  </si>
+  <si>
+    <t>안젤라의 리본</t>
+  </si>
+  <si>
+    <t>천사의 날개깃으로 엮어 만든 성스러운 리본입니다.</t>
+  </si>
+  <si>
+    <t>왕녀의 티아라</t>
+  </si>
+  <si>
+    <t>잊혀진 왕국의 후계자가 쓰던 찬란한 티아라입니다.</t>
+  </si>
+  <si>
+    <t>펠리체의 챙 모자</t>
+  </si>
+  <si>
+    <t>행운을 부른다고 알려진 마법사의 챙 넓은 모자입니다.</t>
+  </si>
+  <si>
+    <t>나비춤의 목걸이</t>
+  </si>
+  <si>
+    <t>은은한 빛무리가 나비처럼 춤추는 환상적인 목걸이입니다.</t>
+  </si>
+  <si>
+    <t>인도자의 목걸이</t>
+  </si>
+  <si>
+    <t>길 잃은 자들을 올바른 곳으로 이끌어주는 나침반 목걸이입니다.</t>
+  </si>
+  <si>
+    <t>증폭의 목걸이</t>
+  </si>
+  <si>
+    <t>착용자의 마력을 극한으로 끌어올리는 위험한 장신구입니다.</t>
+  </si>
+  <si>
+    <t>정열의 펜던트</t>
+  </si>
+  <si>
+    <t>가슴속에 뜨거운 투지를 불어넣는 붉은 보석 펜던트입니다.</t>
+  </si>
+  <si>
+    <t>전사의 반지</t>
+  </si>
+  <si>
+    <t>수많은 전장을 헤쳐온 노련한 전사들의 상징입니다.</t>
+  </si>
+  <si>
+    <t>암살자의 반지</t>
+  </si>
+  <si>
+    <t>어둠 속에서 은밀하게 움직이는 자들을 위한 가벼운 반지입니다.</t>
+  </si>
+  <si>
+    <t>사냥꾼의 반지</t>
+  </si>
+  <si>
+    <t>먹잇감을 절대 놓치지 않는 예리한 사냥꾼의 반지입니다.</t>
+  </si>
+  <si>
+    <t>지휘관의 반지</t>
+  </si>
+  <si>
+    <t>군대를 호령하던 위대한 지휘관의 권위가 담겨 있습니다.</t>
   </si>
 </sst>
 </file>
@@ -444,7 +604,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J2"/>
+  <dimension ref="A1:I19"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="19.875" customWidth="1"/>
@@ -452,12 +612,12 @@
     <col min="4" max="4" width="13.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B1" t="s">
         <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>8</v>
       </c>
       <c r="C1" t="s">
         <v>1</v>
@@ -472,42 +632,535 @@
         <v>4</v>
       </c>
       <c r="G1" t="s">
+        <v>36</v>
+      </c>
+      <c r="H1" t="s">
         <v>5</v>
-      </c>
-      <c r="H1" t="s">
-        <v>13</v>
       </c>
       <c r="I1" t="s">
         <v>6</v>
       </c>
-      <c r="J1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B2">
+        <v>90</v>
+      </c>
+      <c r="C2">
+        <v>450</v>
+      </c>
+      <c r="D2">
+        <v>30</v>
+      </c>
+      <c r="E2" t="s">
+        <v>37</v>
+      </c>
+      <c r="F2" t="s">
+        <v>38</v>
+      </c>
+      <c r="G2" t="s">
+        <v>39</v>
+      </c>
+      <c r="H2" t="s">
+        <v>40</v>
+      </c>
+      <c r="I2" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B3">
+        <v>70</v>
+      </c>
+      <c r="C3">
+        <v>400</v>
+      </c>
+      <c r="D3">
+        <v>0</v>
+      </c>
+      <c r="E3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F3" t="s">
+        <v>43</v>
+      </c>
+      <c r="G3" t="s">
+        <v>44</v>
+      </c>
+      <c r="H3" t="s">
+        <v>40</v>
+      </c>
+      <c r="I3" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
         <v>19</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B4">
+        <v>65</v>
+      </c>
+      <c r="C4">
+        <v>350</v>
+      </c>
+      <c r="D4">
+        <v>0</v>
+      </c>
+      <c r="E4" t="s">
+        <v>46</v>
+      </c>
+      <c r="F4" t="s">
+        <v>47</v>
+      </c>
+      <c r="G4" t="s">
+        <v>44</v>
+      </c>
+      <c r="H4" t="s">
+        <v>40</v>
+      </c>
+      <c r="I4" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
         <v>20</v>
       </c>
-      <c r="C2">
-        <v>10</v>
-      </c>
-      <c r="D2">
-        <v>10</v>
-      </c>
-      <c r="E2">
-        <v>10</v>
-      </c>
-      <c r="F2" t="s">
+      <c r="B5">
+        <v>45</v>
+      </c>
+      <c r="C5">
+        <v>250</v>
+      </c>
+      <c r="D5">
+        <v>0</v>
+      </c>
+      <c r="E5" t="s">
+        <v>48</v>
+      </c>
+      <c r="F5" t="s">
+        <v>49</v>
+      </c>
+      <c r="G5" t="s">
+        <v>16</v>
+      </c>
+      <c r="H5" t="s">
+        <v>40</v>
+      </c>
+      <c r="I5" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
         <v>21</v>
       </c>
-      <c r="G2" t="s">
+      <c r="B6">
+        <v>60</v>
+      </c>
+      <c r="C6">
+        <v>300</v>
+      </c>
+      <c r="D6">
+        <v>150</v>
+      </c>
+      <c r="E6" t="s">
+        <v>51</v>
+      </c>
+      <c r="F6" t="s">
+        <v>52</v>
+      </c>
+      <c r="G6" t="s">
+        <v>39</v>
+      </c>
+      <c r="H6" t="s">
+        <v>40</v>
+      </c>
+      <c r="I6" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
         <v>22</v>
       </c>
-      <c r="H2" t="s">
+      <c r="B7">
+        <v>55</v>
+      </c>
+      <c r="C7">
+        <v>200</v>
+      </c>
+      <c r="D7">
+        <v>50</v>
+      </c>
+      <c r="E7" t="s">
+        <v>53</v>
+      </c>
+      <c r="F7" t="s">
+        <v>54</v>
+      </c>
+      <c r="G7" t="s">
+        <v>44</v>
+      </c>
+      <c r="H7" t="s">
+        <v>40</v>
+      </c>
+      <c r="I7" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
         <v>23</v>
+      </c>
+      <c r="B8">
+        <v>30</v>
+      </c>
+      <c r="C8">
+        <v>150</v>
+      </c>
+      <c r="D8">
+        <v>40</v>
+      </c>
+      <c r="E8" t="s">
+        <v>55</v>
+      </c>
+      <c r="F8" t="s">
+        <v>56</v>
+      </c>
+      <c r="G8" t="s">
+        <v>44</v>
+      </c>
+      <c r="H8" t="s">
+        <v>40</v>
+      </c>
+      <c r="I8" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>24</v>
+      </c>
+      <c r="B9">
+        <v>45</v>
+      </c>
+      <c r="C9">
+        <v>200</v>
+      </c>
+      <c r="D9">
+        <v>60</v>
+      </c>
+      <c r="E9" t="s">
+        <v>57</v>
+      </c>
+      <c r="F9" t="s">
+        <v>58</v>
+      </c>
+      <c r="G9" t="s">
+        <v>39</v>
+      </c>
+      <c r="H9" t="s">
+        <v>40</v>
+      </c>
+      <c r="I9" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>25</v>
+      </c>
+      <c r="B10">
+        <v>50</v>
+      </c>
+      <c r="C10">
+        <v>250</v>
+      </c>
+      <c r="D10">
+        <v>50</v>
+      </c>
+      <c r="E10" t="s">
+        <v>59</v>
+      </c>
+      <c r="F10" t="s">
+        <v>60</v>
+      </c>
+      <c r="G10" t="s">
+        <v>39</v>
+      </c>
+      <c r="H10" t="s">
+        <v>40</v>
+      </c>
+      <c r="I10" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>26</v>
+      </c>
+      <c r="B11">
+        <v>35</v>
+      </c>
+      <c r="C11">
+        <v>180</v>
+      </c>
+      <c r="D11">
+        <v>20</v>
+      </c>
+      <c r="E11" t="s">
+        <v>61</v>
+      </c>
+      <c r="F11" t="s">
+        <v>62</v>
+      </c>
+      <c r="G11" t="s">
+        <v>44</v>
+      </c>
+      <c r="H11" t="s">
+        <v>40</v>
+      </c>
+      <c r="I11" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>27</v>
+      </c>
+      <c r="B12">
+        <v>20</v>
+      </c>
+      <c r="C12">
+        <v>150</v>
+      </c>
+      <c r="D12">
+        <v>80</v>
+      </c>
+      <c r="E12" t="s">
+        <v>63</v>
+      </c>
+      <c r="F12" t="s">
+        <v>64</v>
+      </c>
+      <c r="G12" t="s">
+        <v>39</v>
+      </c>
+      <c r="H12" t="s">
+        <v>40</v>
+      </c>
+      <c r="I12" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>28</v>
+      </c>
+      <c r="B13">
+        <v>15</v>
+      </c>
+      <c r="C13">
+        <v>100</v>
+      </c>
+      <c r="D13">
+        <v>50</v>
+      </c>
+      <c r="E13" t="s">
+        <v>65</v>
+      </c>
+      <c r="F13" t="s">
+        <v>66</v>
+      </c>
+      <c r="G13" t="s">
+        <v>44</v>
+      </c>
+      <c r="H13" t="s">
+        <v>40</v>
+      </c>
+      <c r="I13" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>29</v>
+      </c>
+      <c r="B14">
+        <v>15</v>
+      </c>
+      <c r="C14">
+        <v>80</v>
+      </c>
+      <c r="D14">
+        <v>150</v>
+      </c>
+      <c r="E14" t="s">
+        <v>67</v>
+      </c>
+      <c r="F14" t="s">
+        <v>68</v>
+      </c>
+      <c r="G14" t="s">
+        <v>39</v>
+      </c>
+      <c r="H14" t="s">
+        <v>40</v>
+      </c>
+      <c r="I14" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>30</v>
+      </c>
+      <c r="B15">
+        <v>25</v>
+      </c>
+      <c r="C15">
+        <v>200</v>
+      </c>
+      <c r="D15">
+        <v>0</v>
+      </c>
+      <c r="E15" t="s">
+        <v>69</v>
+      </c>
+      <c r="F15" t="s">
+        <v>70</v>
+      </c>
+      <c r="G15" t="s">
+        <v>44</v>
+      </c>
+      <c r="H15" t="s">
+        <v>40</v>
+      </c>
+      <c r="I15" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>31</v>
+      </c>
+      <c r="B16">
+        <v>25</v>
+      </c>
+      <c r="C16">
+        <v>150</v>
+      </c>
+      <c r="D16">
+        <v>0</v>
+      </c>
+      <c r="E16" t="s">
+        <v>71</v>
+      </c>
+      <c r="F16" t="s">
+        <v>72</v>
+      </c>
+      <c r="G16" t="s">
+        <v>44</v>
+      </c>
+      <c r="H16" t="s">
+        <v>40</v>
+      </c>
+      <c r="I16" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>32</v>
+      </c>
+      <c r="B17">
+        <v>15</v>
+      </c>
+      <c r="C17">
+        <v>80</v>
+      </c>
+      <c r="D17">
+        <v>20</v>
+      </c>
+      <c r="E17" t="s">
+        <v>73</v>
+      </c>
+      <c r="F17" t="s">
+        <v>74</v>
+      </c>
+      <c r="G17" t="s">
+        <v>44</v>
+      </c>
+      <c r="H17" t="s">
+        <v>40</v>
+      </c>
+      <c r="I17" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>33</v>
+      </c>
+      <c r="B18">
+        <v>30</v>
+      </c>
+      <c r="C18">
+        <v>120</v>
+      </c>
+      <c r="D18">
+        <v>30</v>
+      </c>
+      <c r="E18" t="s">
+        <v>75</v>
+      </c>
+      <c r="F18" t="s">
+        <v>76</v>
+      </c>
+      <c r="G18" t="s">
+        <v>39</v>
+      </c>
+      <c r="H18" t="s">
+        <v>40</v>
+      </c>
+      <c r="I18" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>34</v>
+      </c>
+      <c r="B19">
+        <v>40</v>
+      </c>
+      <c r="C19">
+        <v>250</v>
+      </c>
+      <c r="D19">
+        <v>50</v>
+      </c>
+      <c r="E19" t="s">
+        <v>77</v>
+      </c>
+      <c r="F19" t="s">
+        <v>78</v>
+      </c>
+      <c r="G19" t="s">
+        <v>39</v>
+      </c>
+      <c r="H19" t="s">
+        <v>40</v>
+      </c>
+      <c r="I19" t="s">
+        <v>41</v>
       </c>
     </row>
   </sheetData>
@@ -516,14 +1169,14 @@
     <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="중복된 ID (RowName Error)" error="이미 존재하는 ID입니다!_x000a__x000a_RowName(행 이름)은 고유해야 합니다._x000a_(같은 이름을 두 번 쓸 수 없습니다.)_x000a__x000a_다른 이름을 입력해주세요." sqref="A1:A1048576">
       <formula1>COUNTIF($A:$A, A1) &lt;= 1</formula1>
     </dataValidation>
-    <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="숫자 입력 확인" error="오직 숫자(소수점 가능)만 입력할 수 있습니다." sqref="D2:D1048576 C2:C1048576 E2:E1048576">
+    <dataValidation type="textLength" operator="lessThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="글자 수 초과 (DisplayName)" error="_x000a_아이템 이름이 너무 깁니다! (최대 20자)_x000a__x000a_UI 텍스트 박스를 넘어갈 위험이 있습니다._x000a_더 짧게 줄이거나, 줄바꿈이 필요한지 확인해주세요." sqref="E1">
+      <formula1>20</formula1>
+    </dataValidation>
+    <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="숫자 입력 확인" error="오직 숫자(소수점 가능)만 입력할 수 있습니다." sqref="C20:E1048576 B2:D19">
       <formula1>-1000000</formula1>
       <formula2>1000000</formula2>
     </dataValidation>
-    <dataValidation type="textLength" operator="lessThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="글자 수 초과 (DisplayName)" error="_x000a_아이템 이름이 너무 깁니다! (최대 20자)_x000a__x000a_UI 텍스트 박스를 넘어갈 위험이 있습니다._x000a_더 짧게 줄이거나, 줄바꿈이 필요한지 확인해주세요." sqref="F1">
-      <formula1>20</formula1>
-    </dataValidation>
-    <dataValidation type="textLength" operator="lessThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="설명 길이 확인" error="설명이 너무 깁니다. (100자 제한)_x000a__x000a_※ 팁:_x000a_줄바꿈이 필요하면 [Alt + Enter]를 사용하세요._x000a_너무 긴 설명은 툴팁 가독성을 해칩니다." sqref="G1:G1048576">
+    <dataValidation type="textLength" operator="lessThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="설명 길이 확인" error="설명이 너무 깁니다. (100자 제한)_x000a__x000a_※ 팁:_x000a_줄바꿈이 필요하면 [Alt + Enter]를 사용하세요._x000a_너무 긴 설명은 툴팁 가독성을 해칩니다." sqref="G20:G1048576 F1:F19">
       <formula1>100</formula1>
     </dataValidation>
   </dataValidations>
@@ -535,13 +1188,13 @@
           <x14:formula1>
             <xm:f>Tags!$A$25:$A$28</xm:f>
           </x14:formula1>
-          <xm:sqref>B2:B1048576</xm:sqref>
+          <xm:sqref>B20:B1048576</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="선택 오류" error="목록에 없는 값입니다! 드롭다운(▼)을 눌러서 선택해주세요.">
           <x14:formula1>
             <xm:f>Rarity!$A$1:$A$5</xm:f>
           </x14:formula1>
-          <xm:sqref>H2:H1048576</xm:sqref>
+          <xm:sqref>H20:H1048576 G2:G19</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -556,27 +1209,27 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -592,22 +1245,22 @@
   <sheetData>
     <row r="25" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>

--- a/DesignData/Excel_Masters/ArmorStats_Master.xlsx
+++ b/DesignData/Excel_Masters/ArmorStats_Master.xlsx
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="81">
   <si>
     <t>DefensePower</t>
   </si>
@@ -187,9 +187,6 @@
     <t>거친 황무지를 누비는 자들이 입는 질긴 가죽옷입니다.</t>
   </si>
   <si>
-    <t>Cost_Normal</t>
-  </si>
-  <si>
     <t>주교의 로브</t>
   </si>
   <si>
@@ -272,6 +269,15 @@
   </si>
   <si>
     <t>군대를 호령하던 위대한 지휘관의 권위가 담겨 있습니다.</t>
+  </si>
+  <si>
+    <t>Cost_Common</t>
+  </si>
+  <si>
+    <t>Legendary</t>
+  </si>
+  <si>
+    <t>Cost_Legendary</t>
   </si>
 </sst>
 </file>
@@ -617,550 +623,550 @@
         <v>35</v>
       </c>
       <c r="B1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1" t="s">
+        <v>36</v>
+      </c>
+      <c r="E1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" t="s">
+      <c r="H1" t="s">
         <v>1</v>
       </c>
-      <c r="D1" t="s">
+      <c r="I1" t="s">
         <v>2</v>
-      </c>
-      <c r="E1" t="s">
-        <v>3</v>
-      </c>
-      <c r="F1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G1" t="s">
-        <v>36</v>
-      </c>
-      <c r="H1" t="s">
-        <v>5</v>
-      </c>
-      <c r="I1" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>17</v>
-      </c>
-      <c r="B2">
-        <v>90</v>
-      </c>
-      <c r="C2">
-        <v>450</v>
-      </c>
-      <c r="D2">
-        <v>30</v>
+        <v>20</v>
+      </c>
+      <c r="B2" t="s">
+        <v>48</v>
+      </c>
+      <c r="C2" t="s">
+        <v>49</v>
+      </c>
+      <c r="D2" t="s">
+        <v>16</v>
       </c>
       <c r="E2" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="F2" t="s">
-        <v>38</v>
-      </c>
-      <c r="G2" t="s">
-        <v>39</v>
-      </c>
-      <c r="H2" t="s">
-        <v>40</v>
-      </c>
-      <c r="I2" t="s">
-        <v>41</v>
+        <v>78</v>
+      </c>
+      <c r="G2">
+        <v>45</v>
+      </c>
+      <c r="H2">
+        <v>250</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B3">
-        <v>70</v>
-      </c>
-      <c r="C3">
-        <v>400</v>
-      </c>
-      <c r="D3">
-        <v>0</v>
+        <v>22</v>
+      </c>
+      <c r="B3" t="s">
+        <v>52</v>
+      </c>
+      <c r="C3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D3" t="s">
+        <v>44</v>
       </c>
       <c r="E3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F3" t="s">
-        <v>43</v>
-      </c>
-      <c r="G3" t="s">
-        <v>44</v>
-      </c>
-      <c r="H3" t="s">
-        <v>40</v>
-      </c>
-      <c r="I3" t="s">
         <v>45</v>
+      </c>
+      <c r="G3">
+        <v>55</v>
+      </c>
+      <c r="H3">
+        <v>200</v>
+      </c>
+      <c r="I3">
+        <v>50</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>19</v>
       </c>
-      <c r="B4">
+      <c r="B4" t="s">
+        <v>46</v>
+      </c>
+      <c r="C4" t="s">
+        <v>47</v>
+      </c>
+      <c r="D4" t="s">
+        <v>44</v>
+      </c>
+      <c r="E4" t="s">
+        <v>40</v>
+      </c>
+      <c r="F4" t="s">
+        <v>45</v>
+      </c>
+      <c r="G4">
         <v>65</v>
       </c>
-      <c r="C4">
+      <c r="H4">
         <v>350</v>
       </c>
-      <c r="D4">
+      <c r="I4">
         <v>0</v>
-      </c>
-      <c r="E4" t="s">
-        <v>46</v>
-      </c>
-      <c r="F4" t="s">
-        <v>47</v>
-      </c>
-      <c r="G4" t="s">
-        <v>44</v>
-      </c>
-      <c r="H4" t="s">
-        <v>40</v>
-      </c>
-      <c r="I4" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>20</v>
-      </c>
-      <c r="B5">
+        <v>18</v>
+      </c>
+      <c r="B5" t="s">
+        <v>42</v>
+      </c>
+      <c r="C5" t="s">
+        <v>43</v>
+      </c>
+      <c r="D5" t="s">
+        <v>44</v>
+      </c>
+      <c r="E5" t="s">
+        <v>40</v>
+      </c>
+      <c r="F5" t="s">
         <v>45</v>
       </c>
-      <c r="C5">
-        <v>250</v>
-      </c>
-      <c r="D5">
+      <c r="G5">
+        <v>70</v>
+      </c>
+      <c r="H5">
+        <v>400</v>
+      </c>
+      <c r="I5">
         <v>0</v>
-      </c>
-      <c r="E5" t="s">
-        <v>48</v>
-      </c>
-      <c r="F5" t="s">
-        <v>49</v>
-      </c>
-      <c r="G5" t="s">
-        <v>16</v>
-      </c>
-      <c r="H5" t="s">
-        <v>40</v>
-      </c>
-      <c r="I5" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>21</v>
       </c>
-      <c r="B6">
+      <c r="B6" t="s">
+        <v>50</v>
+      </c>
+      <c r="C6" t="s">
+        <v>51</v>
+      </c>
+      <c r="D6" t="s">
+        <v>39</v>
+      </c>
+      <c r="E6" t="s">
+        <v>40</v>
+      </c>
+      <c r="F6" t="s">
+        <v>41</v>
+      </c>
+      <c r="G6">
         <v>60</v>
       </c>
-      <c r="C6">
+      <c r="H6">
         <v>300</v>
       </c>
-      <c r="D6">
+      <c r="I6">
         <v>150</v>
-      </c>
-      <c r="E6" t="s">
-        <v>51</v>
-      </c>
-      <c r="F6" t="s">
-        <v>52</v>
-      </c>
-      <c r="G6" t="s">
-        <v>39</v>
-      </c>
-      <c r="H6" t="s">
-        <v>40</v>
-      </c>
-      <c r="I6" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>22</v>
-      </c>
-      <c r="B7">
-        <v>55</v>
-      </c>
-      <c r="C7">
-        <v>200</v>
-      </c>
-      <c r="D7">
+        <v>17</v>
+      </c>
+      <c r="B7" t="s">
+        <v>37</v>
+      </c>
+      <c r="C7" t="s">
+        <v>38</v>
+      </c>
+      <c r="D7" t="s">
+        <v>79</v>
+      </c>
+      <c r="E7" t="s">
+        <v>40</v>
+      </c>
+      <c r="F7" t="s">
+        <v>80</v>
+      </c>
+      <c r="G7">
+        <v>120</v>
+      </c>
+      <c r="H7">
+        <v>600</v>
+      </c>
+      <c r="I7">
         <v>50</v>
-      </c>
-      <c r="E7" t="s">
-        <v>53</v>
-      </c>
-      <c r="F7" t="s">
-        <v>54</v>
-      </c>
-      <c r="G7" t="s">
-        <v>44</v>
-      </c>
-      <c r="H7" t="s">
-        <v>40</v>
-      </c>
-      <c r="I7" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>23</v>
       </c>
-      <c r="B8">
+      <c r="B8" t="s">
+        <v>54</v>
+      </c>
+      <c r="C8" t="s">
+        <v>55</v>
+      </c>
+      <c r="D8" t="s">
+        <v>44</v>
+      </c>
+      <c r="E8" t="s">
+        <v>40</v>
+      </c>
+      <c r="F8" t="s">
+        <v>45</v>
+      </c>
+      <c r="G8">
         <v>30</v>
       </c>
-      <c r="C8">
+      <c r="H8">
         <v>150</v>
       </c>
-      <c r="D8">
-        <v>40</v>
-      </c>
-      <c r="E8" t="s">
-        <v>55</v>
-      </c>
-      <c r="F8" t="s">
-        <v>56</v>
-      </c>
-      <c r="G8" t="s">
-        <v>44</v>
-      </c>
-      <c r="H8" t="s">
-        <v>40</v>
-      </c>
-      <c r="I8" t="s">
-        <v>45</v>
+      <c r="I8">
+        <v>40</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>24</v>
-      </c>
-      <c r="B9">
+        <v>26</v>
+      </c>
+      <c r="B9" t="s">
+        <v>60</v>
+      </c>
+      <c r="C9" t="s">
+        <v>61</v>
+      </c>
+      <c r="D9" t="s">
+        <v>44</v>
+      </c>
+      <c r="E9" t="s">
+        <v>40</v>
+      </c>
+      <c r="F9" t="s">
         <v>45</v>
       </c>
-      <c r="C9">
-        <v>200</v>
-      </c>
-      <c r="D9">
-        <v>60</v>
-      </c>
-      <c r="E9" t="s">
-        <v>57</v>
-      </c>
-      <c r="F9" t="s">
-        <v>58</v>
-      </c>
-      <c r="G9" t="s">
-        <v>39</v>
-      </c>
-      <c r="H9" t="s">
-        <v>40</v>
-      </c>
-      <c r="I9" t="s">
-        <v>41</v>
+      <c r="G9">
+        <v>35</v>
+      </c>
+      <c r="H9">
+        <v>180</v>
+      </c>
+      <c r="I9">
+        <v>20</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>25</v>
-      </c>
-      <c r="B10">
-        <v>50</v>
-      </c>
-      <c r="C10">
-        <v>250</v>
-      </c>
-      <c r="D10">
-        <v>50</v>
+        <v>24</v>
+      </c>
+      <c r="B10" t="s">
+        <v>56</v>
+      </c>
+      <c r="C10" t="s">
+        <v>57</v>
+      </c>
+      <c r="D10" t="s">
+        <v>39</v>
       </c>
       <c r="E10" t="s">
-        <v>59</v>
+        <v>40</v>
       </c>
       <c r="F10" t="s">
+        <v>41</v>
+      </c>
+      <c r="G10">
+        <v>45</v>
+      </c>
+      <c r="H10">
+        <v>200</v>
+      </c>
+      <c r="I10">
         <v>60</v>
-      </c>
-      <c r="G10" t="s">
-        <v>39</v>
-      </c>
-      <c r="H10" t="s">
-        <v>40</v>
-      </c>
-      <c r="I10" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>26</v>
-      </c>
-      <c r="B11">
-        <v>35</v>
-      </c>
-      <c r="C11">
-        <v>180</v>
-      </c>
-      <c r="D11">
-        <v>20</v>
+        <v>25</v>
+      </c>
+      <c r="B11" t="s">
+        <v>58</v>
+      </c>
+      <c r="C11" t="s">
+        <v>59</v>
+      </c>
+      <c r="D11" t="s">
+        <v>79</v>
       </c>
       <c r="E11" t="s">
-        <v>61</v>
+        <v>40</v>
       </c>
       <c r="F11" t="s">
-        <v>62</v>
-      </c>
-      <c r="G11" t="s">
-        <v>44</v>
-      </c>
-      <c r="H11" t="s">
-        <v>40</v>
-      </c>
-      <c r="I11" t="s">
-        <v>45</v>
+        <v>80</v>
+      </c>
+      <c r="G11">
+        <v>70</v>
+      </c>
+      <c r="H11">
+        <v>350</v>
+      </c>
+      <c r="I11">
+        <v>80</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>27</v>
-      </c>
-      <c r="B12">
-        <v>20</v>
-      </c>
-      <c r="C12">
-        <v>150</v>
-      </c>
-      <c r="D12">
-        <v>80</v>
+        <v>28</v>
+      </c>
+      <c r="B12" t="s">
+        <v>64</v>
+      </c>
+      <c r="C12" t="s">
+        <v>65</v>
+      </c>
+      <c r="D12" t="s">
+        <v>44</v>
       </c>
       <c r="E12" t="s">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="F12" t="s">
-        <v>64</v>
-      </c>
-      <c r="G12" t="s">
-        <v>39</v>
-      </c>
-      <c r="H12" t="s">
-        <v>40</v>
-      </c>
-      <c r="I12" t="s">
-        <v>41</v>
+        <v>45</v>
+      </c>
+      <c r="G12">
+        <v>15</v>
+      </c>
+      <c r="H12">
+        <v>100</v>
+      </c>
+      <c r="I12">
+        <v>50</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>28</v>
-      </c>
-      <c r="B13">
-        <v>15</v>
-      </c>
-      <c r="C13">
-        <v>100</v>
-      </c>
-      <c r="D13">
-        <v>50</v>
+        <v>30</v>
+      </c>
+      <c r="B13" t="s">
+        <v>68</v>
+      </c>
+      <c r="C13" t="s">
+        <v>69</v>
+      </c>
+      <c r="D13" t="s">
+        <v>44</v>
       </c>
       <c r="E13" t="s">
-        <v>65</v>
+        <v>40</v>
       </c>
       <c r="F13" t="s">
-        <v>66</v>
-      </c>
-      <c r="G13" t="s">
-        <v>44</v>
-      </c>
-      <c r="H13" t="s">
-        <v>40</v>
-      </c>
-      <c r="I13" t="s">
         <v>45</v>
+      </c>
+      <c r="G13">
+        <v>25</v>
+      </c>
+      <c r="H13">
+        <v>200</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>29</v>
       </c>
-      <c r="B14">
+      <c r="B14" t="s">
+        <v>66</v>
+      </c>
+      <c r="C14" t="s">
+        <v>67</v>
+      </c>
+      <c r="D14" t="s">
+        <v>39</v>
+      </c>
+      <c r="E14" t="s">
+        <v>40</v>
+      </c>
+      <c r="F14" t="s">
+        <v>41</v>
+      </c>
+      <c r="G14">
         <v>15</v>
       </c>
-      <c r="C14">
+      <c r="H14">
         <v>80</v>
       </c>
-      <c r="D14">
+      <c r="I14">
         <v>150</v>
-      </c>
-      <c r="E14" t="s">
-        <v>67</v>
-      </c>
-      <c r="F14" t="s">
-        <v>68</v>
-      </c>
-      <c r="G14" t="s">
-        <v>39</v>
-      </c>
-      <c r="H14" t="s">
-        <v>40</v>
-      </c>
-      <c r="I14" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
+        <v>27</v>
+      </c>
+      <c r="B15" t="s">
+        <v>62</v>
+      </c>
+      <c r="C15" t="s">
+        <v>63</v>
+      </c>
+      <c r="D15" t="s">
+        <v>79</v>
+      </c>
+      <c r="E15" t="s">
+        <v>40</v>
+      </c>
+      <c r="F15" t="s">
+        <v>80</v>
+      </c>
+      <c r="G15">
         <v>30</v>
       </c>
-      <c r="B15">
-        <v>25</v>
-      </c>
-      <c r="C15">
-        <v>200</v>
-      </c>
-      <c r="D15">
-        <v>0</v>
-      </c>
-      <c r="E15" t="s">
-        <v>69</v>
-      </c>
-      <c r="F15" t="s">
-        <v>70</v>
-      </c>
-      <c r="G15" t="s">
-        <v>44</v>
-      </c>
-      <c r="H15" t="s">
-        <v>40</v>
-      </c>
-      <c r="I15" t="s">
-        <v>45</v>
+      <c r="H15">
+        <v>250</v>
+      </c>
+      <c r="I15">
+        <v>120</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>31</v>
-      </c>
-      <c r="B16">
-        <v>25</v>
-      </c>
-      <c r="C16">
-        <v>150</v>
-      </c>
-      <c r="D16">
-        <v>0</v>
+        <v>32</v>
+      </c>
+      <c r="B16" t="s">
+        <v>72</v>
+      </c>
+      <c r="C16" t="s">
+        <v>73</v>
+      </c>
+      <c r="D16" t="s">
+        <v>44</v>
       </c>
       <c r="E16" t="s">
-        <v>71</v>
+        <v>40</v>
       </c>
       <c r="F16" t="s">
-        <v>72</v>
-      </c>
-      <c r="G16" t="s">
-        <v>44</v>
-      </c>
-      <c r="H16" t="s">
-        <v>40</v>
-      </c>
-      <c r="I16" t="s">
         <v>45</v>
+      </c>
+      <c r="G16">
+        <v>15</v>
+      </c>
+      <c r="H16">
+        <v>80</v>
+      </c>
+      <c r="I16">
+        <v>20</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>32</v>
-      </c>
-      <c r="B17">
-        <v>15</v>
-      </c>
-      <c r="C17">
-        <v>80</v>
-      </c>
-      <c r="D17">
-        <v>20</v>
+        <v>31</v>
+      </c>
+      <c r="B17" t="s">
+        <v>70</v>
+      </c>
+      <c r="C17" t="s">
+        <v>71</v>
+      </c>
+      <c r="D17" t="s">
+        <v>44</v>
       </c>
       <c r="E17" t="s">
-        <v>73</v>
+        <v>40</v>
       </c>
       <c r="F17" t="s">
-        <v>74</v>
-      </c>
-      <c r="G17" t="s">
-        <v>44</v>
-      </c>
-      <c r="H17" t="s">
-        <v>40</v>
-      </c>
-      <c r="I17" t="s">
         <v>45</v>
+      </c>
+      <c r="G17">
+        <v>25</v>
+      </c>
+      <c r="H17">
+        <v>150</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>33</v>
       </c>
-      <c r="B18">
+      <c r="B18" t="s">
+        <v>74</v>
+      </c>
+      <c r="C18" t="s">
+        <v>75</v>
+      </c>
+      <c r="D18" t="s">
+        <v>39</v>
+      </c>
+      <c r="E18" t="s">
+        <v>40</v>
+      </c>
+      <c r="F18" t="s">
+        <v>41</v>
+      </c>
+      <c r="G18">
         <v>30</v>
       </c>
-      <c r="C18">
+      <c r="H18">
         <v>120</v>
       </c>
-      <c r="D18">
+      <c r="I18">
         <v>30</v>
-      </c>
-      <c r="E18" t="s">
-        <v>75</v>
-      </c>
-      <c r="F18" t="s">
-        <v>76</v>
-      </c>
-      <c r="G18" t="s">
-        <v>39</v>
-      </c>
-      <c r="H18" t="s">
-        <v>40</v>
-      </c>
-      <c r="I18" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>34</v>
       </c>
-      <c r="B19">
-        <v>40</v>
-      </c>
-      <c r="C19">
-        <v>250</v>
-      </c>
-      <c r="D19">
-        <v>50</v>
+      <c r="B19" t="s">
+        <v>76</v>
+      </c>
+      <c r="C19" t="s">
+        <v>77</v>
+      </c>
+      <c r="D19" t="s">
+        <v>79</v>
       </c>
       <c r="E19" t="s">
-        <v>77</v>
+        <v>40</v>
       </c>
       <c r="F19" t="s">
-        <v>78</v>
-      </c>
-      <c r="G19" t="s">
-        <v>39</v>
-      </c>
-      <c r="H19" t="s">
-        <v>40</v>
-      </c>
-      <c r="I19" t="s">
-        <v>41</v>
+        <v>80</v>
+      </c>
+      <c r="G19">
+        <v>60</v>
+      </c>
+      <c r="H19">
+        <v>350</v>
+      </c>
+      <c r="I19">
+        <v>80</v>
       </c>
     </row>
   </sheetData>

--- a/DesignData/Excel_Masters/ArmorStats_Master.xlsx
+++ b/DesignData/Excel_Masters/ArmorStats_Master.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="76">
   <si>
     <t>---</t>
   </si>
@@ -241,6 +241,12 @@
   </si>
   <si>
     <t>군대를 호령하던 위대한 지휘관의 권위가 담겨 있습니다.</t>
+  </si>
+  <si>
+    <t>HealthRegen</t>
+  </si>
+  <si>
+    <t>ManaRegen</t>
   </si>
 </sst>
 </file>
@@ -1158,10 +1164,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I19"/>
+  <dimension ref="A1:K19"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1175,22 +1181,28 @@
         <v>3</v>
       </c>
       <c r="E1" t="s">
+        <v>74</v>
+      </c>
+      <c r="F1" t="s">
+        <v>75</v>
+      </c>
+      <c r="G1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="H1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="I1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="J1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="K1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -1203,23 +1215,29 @@
       <c r="D2">
         <v>0</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2" t="s">
         <v>38</v>
       </c>
-      <c r="F2" t="s">
+      <c r="H2" t="s">
         <v>56</v>
       </c>
-      <c r="G2" t="s">
+      <c r="I2" t="s">
         <v>10</v>
       </c>
-      <c r="H2" t="s">
+      <c r="J2" t="s">
         <v>11</v>
       </c>
-      <c r="I2" t="s">
+      <c r="K2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>13</v>
       </c>
@@ -1232,23 +1250,29 @@
       <c r="D3">
         <v>50</v>
       </c>
-      <c r="E3" t="s">
+      <c r="E3">
+        <v>0</v>
+      </c>
+      <c r="F3">
+        <v>0</v>
+      </c>
+      <c r="G3" t="s">
         <v>39</v>
       </c>
-      <c r="F3" t="s">
+      <c r="H3" t="s">
         <v>57</v>
       </c>
-      <c r="G3" t="s">
+      <c r="I3" t="s">
         <v>14</v>
       </c>
-      <c r="H3" t="s">
+      <c r="J3" t="s">
         <v>15</v>
       </c>
-      <c r="I3" t="s">
+      <c r="K3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>17</v>
       </c>
@@ -1261,23 +1285,29 @@
       <c r="D4">
         <v>0</v>
       </c>
-      <c r="E4" t="s">
+      <c r="E4">
+        <v>0</v>
+      </c>
+      <c r="F4">
+        <v>0</v>
+      </c>
+      <c r="G4" t="s">
         <v>40</v>
       </c>
-      <c r="F4" t="s">
+      <c r="H4" t="s">
         <v>58</v>
       </c>
-      <c r="G4" t="s">
+      <c r="I4" t="s">
         <v>14</v>
       </c>
-      <c r="H4" t="s">
+      <c r="J4" t="s">
         <v>15</v>
       </c>
-      <c r="I4" t="s">
+      <c r="K4" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>18</v>
       </c>
@@ -1290,23 +1320,29 @@
       <c r="D5">
         <v>0</v>
       </c>
-      <c r="E5" t="s">
+      <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5">
+        <v>0</v>
+      </c>
+      <c r="G5" t="s">
         <v>41</v>
       </c>
-      <c r="F5" t="s">
+      <c r="H5" t="s">
         <v>59</v>
       </c>
-      <c r="G5" t="s">
+      <c r="I5" t="s">
         <v>14</v>
       </c>
-      <c r="H5" t="s">
+      <c r="J5" t="s">
         <v>15</v>
       </c>
-      <c r="I5" t="s">
+      <c r="K5" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>19</v>
       </c>
@@ -1319,23 +1355,29 @@
       <c r="D6">
         <v>150</v>
       </c>
-      <c r="E6" t="s">
+      <c r="E6">
+        <v>0</v>
+      </c>
+      <c r="F6">
+        <v>0</v>
+      </c>
+      <c r="G6" t="s">
         <v>42</v>
       </c>
-      <c r="F6" t="s">
+      <c r="H6" t="s">
         <v>60</v>
       </c>
-      <c r="G6" t="s">
+      <c r="I6" t="s">
         <v>20</v>
       </c>
-      <c r="H6" t="s">
+      <c r="J6" t="s">
         <v>15</v>
       </c>
-      <c r="I6" t="s">
+      <c r="K6" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>22</v>
       </c>
@@ -1348,23 +1390,29 @@
       <c r="D7">
         <v>50</v>
       </c>
-      <c r="E7" t="s">
+      <c r="E7">
+        <v>0</v>
+      </c>
+      <c r="F7">
+        <v>0</v>
+      </c>
+      <c r="G7" t="s">
         <v>43</v>
       </c>
-      <c r="F7" t="s">
+      <c r="H7" t="s">
         <v>61</v>
       </c>
-      <c r="G7" t="s">
+      <c r="I7" t="s">
         <v>23</v>
       </c>
-      <c r="H7" t="s">
+      <c r="J7" t="s">
         <v>15</v>
       </c>
-      <c r="I7" t="s">
+      <c r="K7" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>25</v>
       </c>
@@ -1377,23 +1425,29 @@
       <c r="D8">
         <v>40</v>
       </c>
-      <c r="E8" t="s">
+      <c r="E8">
+        <v>0</v>
+      </c>
+      <c r="F8">
+        <v>0</v>
+      </c>
+      <c r="G8" t="s">
         <v>44</v>
       </c>
-      <c r="F8" t="s">
+      <c r="H8" t="s">
         <v>62</v>
       </c>
-      <c r="G8" t="s">
+      <c r="I8" t="s">
         <v>14</v>
       </c>
-      <c r="H8" t="s">
+      <c r="J8" t="s">
         <v>11</v>
       </c>
-      <c r="I8" t="s">
+      <c r="K8" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>26</v>
       </c>
@@ -1406,23 +1460,29 @@
       <c r="D9">
         <v>20</v>
       </c>
-      <c r="E9" t="s">
+      <c r="E9">
+        <v>0</v>
+      </c>
+      <c r="F9">
+        <v>0</v>
+      </c>
+      <c r="G9" t="s">
         <v>45</v>
       </c>
-      <c r="F9" t="s">
+      <c r="H9" t="s">
         <v>63</v>
       </c>
-      <c r="G9" t="s">
+      <c r="I9" t="s">
         <v>27</v>
       </c>
-      <c r="H9" t="s">
+      <c r="J9" t="s">
         <v>15</v>
       </c>
-      <c r="I9" t="s">
+      <c r="K9" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>28</v>
       </c>
@@ -1435,23 +1495,29 @@
       <c r="D10">
         <v>60</v>
       </c>
-      <c r="E10" t="s">
+      <c r="E10">
+        <v>0</v>
+      </c>
+      <c r="F10">
+        <v>0</v>
+      </c>
+      <c r="G10" t="s">
         <v>46</v>
       </c>
-      <c r="F10" t="s">
+      <c r="H10" t="s">
         <v>64</v>
       </c>
-      <c r="G10" t="s">
+      <c r="I10" t="s">
         <v>20</v>
       </c>
-      <c r="H10" t="s">
+      <c r="J10" t="s">
         <v>15</v>
       </c>
-      <c r="I10" t="s">
+      <c r="K10" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>29</v>
       </c>
@@ -1464,23 +1530,29 @@
       <c r="D11">
         <v>80</v>
       </c>
-      <c r="E11" t="s">
+      <c r="E11">
+        <v>0</v>
+      </c>
+      <c r="F11">
+        <v>0</v>
+      </c>
+      <c r="G11" t="s">
         <v>47</v>
       </c>
-      <c r="F11" t="s">
+      <c r="H11" t="s">
         <v>65</v>
       </c>
-      <c r="G11" t="s">
+      <c r="I11" t="s">
         <v>23</v>
       </c>
-      <c r="H11" t="s">
+      <c r="J11" t="s">
         <v>15</v>
       </c>
-      <c r="I11" t="s">
+      <c r="K11" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>30</v>
       </c>
@@ -1493,23 +1565,29 @@
       <c r="D12">
         <v>50</v>
       </c>
-      <c r="E12" t="s">
+      <c r="E12">
+        <v>0</v>
+      </c>
+      <c r="F12">
+        <v>0</v>
+      </c>
+      <c r="G12" t="s">
         <v>48</v>
       </c>
-      <c r="F12" t="s">
+      <c r="H12" t="s">
         <v>66</v>
       </c>
-      <c r="G12" t="s">
+      <c r="I12" t="s">
         <v>27</v>
       </c>
-      <c r="H12" t="s">
+      <c r="J12" t="s">
         <v>11</v>
       </c>
-      <c r="I12" t="s">
+      <c r="K12" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>31</v>
       </c>
@@ -1522,23 +1600,29 @@
       <c r="D13">
         <v>0</v>
       </c>
-      <c r="E13" t="s">
+      <c r="E13">
+        <v>0</v>
+      </c>
+      <c r="F13">
+        <v>0</v>
+      </c>
+      <c r="G13" t="s">
         <v>49</v>
       </c>
-      <c r="F13" t="s">
+      <c r="H13" t="s">
         <v>67</v>
       </c>
-      <c r="G13" t="s">
+      <c r="I13" t="s">
         <v>14</v>
       </c>
-      <c r="H13" t="s">
+      <c r="J13" t="s">
         <v>15</v>
       </c>
-      <c r="I13" t="s">
+      <c r="K13" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>32</v>
       </c>
@@ -1551,23 +1635,29 @@
       <c r="D14">
         <v>150</v>
       </c>
-      <c r="E14" t="s">
+      <c r="E14">
+        <v>0</v>
+      </c>
+      <c r="F14">
+        <v>0</v>
+      </c>
+      <c r="G14" t="s">
         <v>50</v>
       </c>
-      <c r="F14" t="s">
+      <c r="H14" t="s">
         <v>68</v>
       </c>
-      <c r="G14" t="s">
+      <c r="I14" t="s">
         <v>20</v>
       </c>
-      <c r="H14" t="s">
+      <c r="J14" t="s">
         <v>15</v>
       </c>
-      <c r="I14" t="s">
+      <c r="K14" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>33</v>
       </c>
@@ -1580,23 +1670,29 @@
       <c r="D15">
         <v>120</v>
       </c>
-      <c r="E15" t="s">
+      <c r="E15">
+        <v>0</v>
+      </c>
+      <c r="F15">
+        <v>0</v>
+      </c>
+      <c r="G15" t="s">
         <v>51</v>
       </c>
-      <c r="F15" t="s">
+      <c r="H15" t="s">
         <v>69</v>
       </c>
-      <c r="G15" t="s">
+      <c r="I15" t="s">
         <v>23</v>
       </c>
-      <c r="H15" t="s">
+      <c r="J15" t="s">
         <v>15</v>
       </c>
-      <c r="I15" t="s">
+      <c r="K15" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>34</v>
       </c>
@@ -1609,23 +1705,29 @@
       <c r="D16">
         <v>20</v>
       </c>
-      <c r="E16" t="s">
+      <c r="E16">
+        <v>0</v>
+      </c>
+      <c r="F16">
+        <v>0</v>
+      </c>
+      <c r="G16" t="s">
         <v>52</v>
       </c>
-      <c r="F16" t="s">
+      <c r="H16" t="s">
         <v>70</v>
       </c>
-      <c r="G16" t="s">
+      <c r="I16" t="s">
         <v>14</v>
       </c>
-      <c r="H16" t="s">
+      <c r="J16" t="s">
         <v>11</v>
       </c>
-      <c r="I16" t="s">
+      <c r="K16" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>35</v>
       </c>
@@ -1638,23 +1740,29 @@
       <c r="D17">
         <v>0</v>
       </c>
-      <c r="E17" t="s">
+      <c r="E17">
+        <v>0</v>
+      </c>
+      <c r="F17">
+        <v>0</v>
+      </c>
+      <c r="G17" t="s">
         <v>53</v>
       </c>
-      <c r="F17" t="s">
+      <c r="H17" t="s">
         <v>71</v>
       </c>
-      <c r="G17" t="s">
+      <c r="I17" t="s">
         <v>14</v>
       </c>
-      <c r="H17" t="s">
+      <c r="J17" t="s">
         <v>15</v>
       </c>
-      <c r="I17" t="s">
+      <c r="K17" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>36</v>
       </c>
@@ -1667,23 +1775,29 @@
       <c r="D18">
         <v>30</v>
       </c>
-      <c r="E18" t="s">
+      <c r="E18">
+        <v>0</v>
+      </c>
+      <c r="F18">
+        <v>0</v>
+      </c>
+      <c r="G18" t="s">
         <v>54</v>
       </c>
-      <c r="F18" t="s">
+      <c r="H18" t="s">
         <v>72</v>
       </c>
-      <c r="G18" t="s">
+      <c r="I18" t="s">
         <v>20</v>
       </c>
-      <c r="H18" t="s">
+      <c r="J18" t="s">
         <v>15</v>
       </c>
-      <c r="I18" t="s">
+      <c r="K18" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>37</v>
       </c>
@@ -1696,19 +1810,25 @@
       <c r="D19">
         <v>80</v>
       </c>
-      <c r="E19" t="s">
+      <c r="E19">
+        <v>0</v>
+      </c>
+      <c r="F19">
+        <v>0</v>
+      </c>
+      <c r="G19" t="s">
         <v>55</v>
       </c>
-      <c r="F19" t="s">
+      <c r="H19" t="s">
         <v>73</v>
       </c>
-      <c r="G19" t="s">
+      <c r="I19" t="s">
         <v>23</v>
       </c>
-      <c r="H19" t="s">
+      <c r="J19" t="s">
         <v>15</v>
       </c>
-      <c r="I19" t="s">
+      <c r="K19" t="s">
         <v>24</v>
       </c>
     </row>
